--- a/depend/ship/database.xlsx
+++ b/depend/ship/database.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27615" windowHeight="12885" activeTab="3"/>
+    <workbookView windowWidth="19095" windowHeight="7470" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="舰船数据-未改" sheetId="1" r:id="rId1"/>
@@ -18,15 +18,15 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'舰船数据-未改'!$A$1:$AC$151</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'舰船数据-改造'!$A$1:$AC$226</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'装备数据-常规'!$A$1:$Z$417</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'舰船数据-深海'!$A$1:$AC$367</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'装备数据-深海'!$A$1:$W$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'舰船数据-深海'!$A$1:$AC$368</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'装备数据-深海'!$A$1:$W$64</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6669" uniqueCount="2430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6668" uniqueCount="2429">
   <si>
     <t>cid</t>
   </si>
@@ -7150,7 +7150,7 @@
     <t>03002</t>
   </si>
   <si>
-    <t>Nagara-Class[Fog]</t>
+    <t>Nagara MassProd[Fog]</t>
   </si>
   <si>
     <t>防空导弹作战系统</t>
@@ -7162,19 +7162,19 @@
     <t>03003</t>
   </si>
   <si>
-    <t>Fletcher-Class[Fog]</t>
+    <t>Fletcher MassProd[Fog]</t>
   </si>
   <si>
     <t>03004</t>
   </si>
   <si>
-    <t>Kagerou-Class[Fog]</t>
+    <t>Kagerou MassProd[Fog]</t>
   </si>
   <si>
     <t>03005</t>
   </si>
   <si>
-    <t>CVS</t>
+    <t>Ksi-Class[Fog]</t>
   </si>
   <si>
     <t>S-2反潜机</t>
@@ -7183,9 +7183,6 @@
     <t>E-1预警机</t>
   </si>
   <si>
-    <t>030051</t>
-  </si>
-  <si>
     <t>03006</t>
   </si>
   <si>
@@ -7195,7 +7192,7 @@
     <t>03007</t>
   </si>
   <si>
-    <t>CVA</t>
+    <t>Omicron-Class[Fog]</t>
   </si>
   <si>
     <t>SecondaryGun</t>
@@ -7323,10 +7320,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="23">
     <font>
@@ -7371,13 +7368,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -7387,7 +7377,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="0"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -7417,6 +7407,30 @@
     </font>
     <font>
       <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
@@ -7432,24 +7446,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFA7D00"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -7464,31 +7463,21 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF3F3F76"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C6500"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF006100"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -7496,6 +7485,14 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -7516,7 +7513,163 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -7528,169 +7681,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -7751,17 +7748,41 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </right>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -7792,30 +7813,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
@@ -7825,159 +7822,159 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
       </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
       </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
       </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="12" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -8083,7 +8080,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -82750,7 +82746,7 @@
         <v>2377</v>
       </c>
       <c r="B364" s="14" t="s">
-        <v>92</v>
+        <v>2259</v>
       </c>
       <c r="C364" s="14" t="s">
         <v>2378</v>
@@ -82989,21 +82985,19 @@
       <c r="Z366" s="13">
         <v>10</v>
       </c>
-      <c r="AA366" s="42" t="s">
-        <v>2385</v>
-      </c>
+      <c r="AA366" s="16"/>
       <c r="AB366" s="13"/>
       <c r="AC366" s="13"/>
     </row>
     <row r="367" s="14" customFormat="1" spans="1:26">
       <c r="A367" s="18" t="s">
-        <v>2386</v>
+        <v>2385</v>
       </c>
       <c r="B367" s="14" t="s">
         <v>87</v>
       </c>
       <c r="C367" s="14" t="s">
-        <v>2387</v>
+        <v>2386</v>
       </c>
       <c r="D367" s="14" t="s">
         <v>1617</v>
@@ -83075,13 +83069,13 @@
     </row>
     <row r="368" customFormat="1" spans="1:29">
       <c r="A368" s="18" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="B368" t="s">
         <v>29</v>
       </c>
       <c r="C368" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="D368" t="s">
         <v>1617</v>
@@ -83158,8 +83152,8 @@
       <c r="AC368" s="13"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AC367">
-    <sortState ref="A1:AC367">
+  <autoFilter ref="A1:AC368">
+    <sortState ref="A1:AC368">
       <sortCondition ref="A1:A267"/>
     </sortState>
     <extLst/>
@@ -83499,13 +83493,13 @@
         <v>1647</v>
       </c>
       <c r="B11" t="s">
+        <v>2389</v>
+      </c>
+      <c r="C11" t="s">
         <v>2390</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>2391</v>
-      </c>
-      <c r="D11" t="s">
-        <v>2392</v>
       </c>
       <c r="F11">
         <v>1</v>
@@ -83525,13 +83519,13 @@
         <v>1649</v>
       </c>
       <c r="B12" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="C12" t="s">
-        <v>2393</v>
+        <v>2392</v>
       </c>
       <c r="D12" t="s">
-        <v>2392</v>
+        <v>2391</v>
       </c>
       <c r="F12">
         <v>1</v>
@@ -83548,13 +83542,13 @@
         <v>1651</v>
       </c>
       <c r="B13" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="C13" t="s">
         <v>1720</v>
       </c>
       <c r="D13" t="s">
-        <v>2392</v>
+        <v>2391</v>
       </c>
       <c r="F13">
         <v>7</v>
@@ -83911,7 +83905,7 @@
         <v>451</v>
       </c>
       <c r="C28" t="s">
-        <v>2394</v>
+        <v>2393</v>
       </c>
       <c r="D28" t="s">
         <v>453</v>
@@ -83940,7 +83934,7 @@
         <v>451</v>
       </c>
       <c r="C29" t="s">
-        <v>2395</v>
+        <v>2394</v>
       </c>
       <c r="D29" t="s">
         <v>453</v>
@@ -84091,7 +84085,7 @@
         <v>459</v>
       </c>
       <c r="C34" t="s">
-        <v>2396</v>
+        <v>2395</v>
       </c>
       <c r="D34" t="s">
         <v>461</v>
@@ -84111,7 +84105,7 @@
         <v>459</v>
       </c>
       <c r="C35" t="s">
-        <v>2397</v>
+        <v>2396</v>
       </c>
       <c r="D35" t="s">
         <v>461</v>
@@ -84151,7 +84145,7 @@
         <v>494</v>
       </c>
       <c r="C37" t="s">
-        <v>2398</v>
+        <v>2397</v>
       </c>
       <c r="D37" t="s">
         <v>496</v>
@@ -84174,7 +84168,7 @@
         <v>441</v>
       </c>
       <c r="C38" t="s">
-        <v>2399</v>
+        <v>2398</v>
       </c>
       <c r="D38" t="s">
         <v>443</v>
@@ -84197,7 +84191,7 @@
         <v>441</v>
       </c>
       <c r="C39" t="s">
-        <v>2400</v>
+        <v>2399</v>
       </c>
       <c r="D39" t="s">
         <v>443</v>
@@ -84220,7 +84214,7 @@
         <v>441</v>
       </c>
       <c r="C40" t="s">
-        <v>2401</v>
+        <v>2400</v>
       </c>
       <c r="D40" t="s">
         <v>443</v>
@@ -84243,7 +84237,7 @@
         <v>441</v>
       </c>
       <c r="C41" t="s">
-        <v>2402</v>
+        <v>2401</v>
       </c>
       <c r="D41" t="s">
         <v>443</v>
@@ -84484,7 +84478,7 @@
         <v>1856</v>
       </c>
       <c r="D52" t="s">
-        <v>2403</v>
+        <v>2402</v>
       </c>
       <c r="F52">
         <v>20</v>
@@ -84565,7 +84559,7 @@
         <v>1903</v>
       </c>
       <c r="D55" t="s">
-        <v>2403</v>
+        <v>2402</v>
       </c>
       <c r="F55">
         <v>18</v>
@@ -84797,16 +84791,6 @@
       <c r="D62" s="12" t="s">
         <v>448</v>
       </c>
-      <c r="E62"/>
-      <c r="F62"/>
-      <c r="G62"/>
-      <c r="H62"/>
-      <c r="I62"/>
-      <c r="J62"/>
-      <c r="K62"/>
-      <c r="L62"/>
-      <c r="M62"/>
-      <c r="N62"/>
       <c r="O62">
         <v>13</v>
       </c>
@@ -84816,9 +84800,6 @@
       <c r="Q62">
         <v>1</v>
       </c>
-      <c r="R62"/>
-      <c r="S62"/>
-      <c r="T62"/>
       <c r="U62">
         <v>6</v>
       </c>
@@ -84839,32 +84820,21 @@
       <c r="D63" s="12" t="s">
         <v>510</v>
       </c>
-      <c r="E63"/>
-      <c r="F63"/>
       <c r="G63">
         <v>12</v>
       </c>
-      <c r="H63"/>
-      <c r="I63"/>
       <c r="J63">
         <v>1</v>
       </c>
       <c r="K63">
         <v>1</v>
       </c>
-      <c r="L63"/>
       <c r="M63">
         <v>1</v>
       </c>
-      <c r="N63"/>
-      <c r="O63"/>
-      <c r="P63"/>
       <c r="Q63">
         <v>1</v>
       </c>
-      <c r="R63"/>
-      <c r="S63"/>
-      <c r="T63"/>
       <c r="U63">
         <v>6</v>
       </c>
@@ -84885,28 +84855,15 @@
       <c r="D64" s="12" t="s">
         <v>553</v>
       </c>
-      <c r="E64"/>
-      <c r="F64"/>
-      <c r="G64"/>
-      <c r="H64"/>
-      <c r="I64"/>
-      <c r="J64"/>
-      <c r="K64"/>
-      <c r="L64"/>
       <c r="M64">
         <v>3</v>
       </c>
-      <c r="N64"/>
-      <c r="O64"/>
       <c r="P64">
         <v>12</v>
       </c>
       <c r="Q64">
         <v>1</v>
       </c>
-      <c r="R64"/>
-      <c r="S64"/>
-      <c r="T64"/>
       <c r="U64">
         <v>6</v>
       </c>
@@ -84915,7 +84872,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:W61">
+  <autoFilter ref="A1:W64">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -84952,7 +84909,7 @@
   <sheetData>
     <row r="1" spans="1:44">
       <c r="A1" s="1" t="s">
-        <v>2404</v>
+        <v>2403</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>2</v>
@@ -84961,30 +84918,30 @@
         <v>416</v>
       </c>
       <c r="D1" s="2" t="s">
+        <v>2404</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>2405</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="7" t="s">
         <v>2406</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="M1" s="9" t="s">
         <v>2407</v>
-      </c>
-      <c r="M1" s="9" t="s">
-        <v>2408</v>
       </c>
       <c r="R1" s="11"/>
       <c r="S1" s="7" t="s">
+        <v>2408</v>
+      </c>
+      <c r="Z1" s="9" t="s">
         <v>2409</v>
-      </c>
-      <c r="Z1" s="9" t="s">
-        <v>2410</v>
       </c>
       <c r="AE1" s="11"/>
       <c r="AF1" s="7" t="s">
+        <v>2410</v>
+      </c>
+      <c r="AM1" s="9" t="s">
         <v>2411</v>
-      </c>
-      <c r="AM1" s="9" t="s">
-        <v>2412</v>
       </c>
       <c r="AR1" s="11"/>
     </row>
@@ -84993,10 +84950,10 @@
         <v>1615</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>2412</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>2413</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>2414</v>
       </c>
       <c r="D2" s="2">
         <v>0</v>
@@ -85103,10 +85060,10 @@
         <v>1619</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>2414</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>2415</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>2416</v>
       </c>
       <c r="D3" s="2">
         <v>1</v>
@@ -85216,7 +85173,7 @@
         <v>43</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>2416</v>
+        <v>2415</v>
       </c>
       <c r="D4" s="2">
         <v>2</v>
@@ -85326,7 +85283,7 @@
         <v>68</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>2416</v>
+        <v>2415</v>
       </c>
       <c r="D5" s="2">
         <v>3</v>
@@ -85430,10 +85387,10 @@
         <v>1630</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>2417</v>
+        <v>2416</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>2416</v>
+        <v>2415</v>
       </c>
       <c r="D6" s="2">
         <v>5</v>
@@ -85540,10 +85497,10 @@
         <v>1634</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>2418</v>
+        <v>2417</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>2416</v>
+        <v>2415</v>
       </c>
       <c r="D7" s="2">
         <v>1</v>
@@ -85650,10 +85607,10 @@
         <v>1638</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>2419</v>
+        <v>2418</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>2416</v>
+        <v>2415</v>
       </c>
       <c r="D8" s="2">
         <v>2</v>
@@ -85760,10 +85717,10 @@
         <v>1641</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>2420</v>
+        <v>2419</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>2416</v>
+        <v>2415</v>
       </c>
       <c r="D9" s="2">
         <v>3</v>
@@ -85870,10 +85827,10 @@
         <v>1857</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>2417</v>
+        <v>2416</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>2416</v>
+        <v>2415</v>
       </c>
       <c r="D10" s="2">
         <v>5</v>
@@ -86022,10 +85979,10 @@
         <v>1886</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>2418</v>
+        <v>2417</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>2416</v>
+        <v>2415</v>
       </c>
       <c r="D11" s="2">
         <v>1</v>
@@ -86084,10 +86041,10 @@
         <v>1888</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>2414</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>2415</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>2416</v>
       </c>
       <c r="D12" s="2">
         <v>1</v>
@@ -86149,7 +86106,7 @@
         <v>89</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>2416</v>
+        <v>2415</v>
       </c>
       <c r="D13" s="2">
         <v>1</v>
@@ -86205,13 +86162,13 @@
     </row>
     <row r="14" spans="1:18">
       <c r="A14" s="1" t="s">
-        <v>2421</v>
+        <v>2420</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>2419</v>
+        <v>2418</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>2416</v>
+        <v>2415</v>
       </c>
       <c r="D14" s="2">
         <v>2</v>
@@ -86273,7 +86230,7 @@
         <v>43</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>2416</v>
+        <v>2415</v>
       </c>
       <c r="D15" s="2">
         <v>2</v>
@@ -86335,7 +86292,7 @@
         <v>47</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>2416</v>
+        <v>2415</v>
       </c>
       <c r="D16" s="2">
         <v>2</v>
@@ -86394,10 +86351,10 @@
         <v>1898</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>2420</v>
+        <v>2419</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>2416</v>
+        <v>2415</v>
       </c>
       <c r="D17" s="2">
         <v>3</v>
@@ -86459,7 +86416,7 @@
         <v>68</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>2422</v>
+        <v>2421</v>
       </c>
       <c r="D18" s="2">
         <v>4</v>
@@ -86500,7 +86457,7 @@
         <v>31</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>2422</v>
+        <v>2421</v>
       </c>
       <c r="D19" s="2">
         <v>2</v>
@@ -86538,10 +86495,10 @@
         <v>1906</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>2423</v>
+        <v>2422</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>2422</v>
+        <v>2421</v>
       </c>
       <c r="D20" s="2">
         <v>4</v>
@@ -86579,10 +86536,10 @@
         <v>1908</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>2424</v>
+        <v>2423</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>2416</v>
+        <v>2415</v>
       </c>
       <c r="D21" s="2">
         <v>3</v>
@@ -86641,10 +86598,10 @@
         <v>1910</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>2425</v>
+        <v>2424</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>2416</v>
+        <v>2415</v>
       </c>
       <c r="D22" s="2">
         <v>3</v>
@@ -86700,13 +86657,13 @@
     </row>
     <row r="23" spans="1:18">
       <c r="A23" s="1" t="s">
+        <v>2425</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>2426</v>
       </c>
-      <c r="B23" s="1" t="s">
-        <v>2427</v>
-      </c>
       <c r="C23" s="1" t="s">
-        <v>2416</v>
+        <v>2415</v>
       </c>
       <c r="D23" s="2">
         <v>5</v>
@@ -86762,13 +86719,13 @@
     </row>
     <row r="24" spans="1:18">
       <c r="A24" s="1" t="s">
-        <v>2428</v>
+        <v>2427</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>2427</v>
+        <v>2426</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>2416</v>
+        <v>2415</v>
       </c>
       <c r="D24" s="2">
         <v>5</v>
@@ -86824,13 +86781,13 @@
     </row>
     <row r="25" spans="1:18">
       <c r="A25" s="1" t="s">
-        <v>2429</v>
+        <v>2428</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>2427</v>
+        <v>2426</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>2416</v>
+        <v>2415</v>
       </c>
       <c r="D25" s="2">
         <v>5</v>

--- a/depend/ship/database.xlsx
+++ b/depend/ship/database.xlsx
@@ -7174,7 +7174,7 @@
     <t>03005</t>
   </si>
   <si>
-    <t>Ksi-Class[Fog]</t>
+    <t>Ξ Class[Fog]</t>
   </si>
   <si>
     <t>S-2反潜机</t>
@@ -7192,7 +7192,7 @@
     <t>03007</t>
   </si>
   <si>
-    <t>Omicron-Class[Fog]</t>
+    <t>Ο Class[Fog]</t>
   </si>
   <si>
     <t>SecondaryGun</t>
@@ -7320,10 +7320,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="23">
     <font>
@@ -7368,16 +7368,32 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color theme="0"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFA7D00"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -7406,17 +7422,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF7F7F7F"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -7440,37 +7448,29 @@
     <font>
       <u/>
       <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF9C0006"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF3F3F76"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -7484,15 +7484,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF9C6500"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF3F3F3F"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -7513,7 +7513,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -7531,13 +7543,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -7555,13 +7567,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -7573,19 +7585,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -7603,13 +7639,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -7621,73 +7681,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -7758,16 +7758,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </right>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -7787,41 +7787,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -7836,145 +7801,180 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="12" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -82609,7 +82609,7 @@
         <v>0</v>
       </c>
       <c r="L362" s="14">
-        <v>75</v>
+        <v>120</v>
       </c>
       <c r="M362">
         <v>55</v>
@@ -82764,7 +82764,7 @@
         <v>99</v>
       </c>
       <c r="H364" s="14">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="I364" s="14">
         <v>127</v>
